--- a/research/traditional_assets/database/data/georgia/georgia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/georgia/georgia_bank_money_center.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="E2">
-        <v>0.205</v>
+        <v>0.228</v>
+      </c>
+      <c r="F2">
+        <v>0.147</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>225.3</v>
+        <v>343.6</v>
       </c>
       <c r="L2">
-        <v>0.5280056245605812</v>
+        <v>0.5545513234344739</v>
       </c>
       <c r="M2">
-        <v>34.86</v>
+        <v>89.38</v>
       </c>
       <c r="N2">
-        <v>0.02862068965517241</v>
+        <v>0.05997450177816547</v>
       </c>
       <c r="O2">
-        <v>0.1547270306258322</v>
+        <v>0.260128055878929</v>
       </c>
       <c r="P2">
-        <v>26.7</v>
+        <v>89.38</v>
       </c>
       <c r="Q2">
-        <v>0.02192118226600985</v>
+        <v>0.05997450177816547</v>
       </c>
       <c r="R2">
-        <v>0.118508655126498</v>
+        <v>0.260128055878929</v>
       </c>
       <c r="S2">
-        <v>8.16</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.23407917383821</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>627.8</v>
+        <v>1327.7</v>
       </c>
       <c r="V2">
-        <v>0.5154351395730705</v>
+        <v>0.8908944507817219</v>
       </c>
       <c r="W2">
-        <v>0.263078000934143</v>
+        <v>0.3123068532994001</v>
       </c>
       <c r="X2">
-        <v>0.1074776879605195</v>
+        <v>0.1453327655588968</v>
       </c>
       <c r="Y2">
-        <v>0.1556003129736234</v>
+        <v>0.1669740877405033</v>
       </c>
       <c r="Z2">
-        <v>0.1820780883294218</v>
+        <v>0.2774245544909106</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0683454757985265</v>
+        <v>0.1064471554224178</v>
       </c>
       <c r="AC2">
-        <v>-0.0683454757985265</v>
+        <v>-0.1064471554224178</v>
       </c>
       <c r="AD2">
-        <v>1780.2</v>
+        <v>2040.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1780.2</v>
+        <v>2040.2</v>
       </c>
       <c r="AG2">
-        <v>1152.4</v>
+        <v>712.5</v>
       </c>
       <c r="AH2">
-        <v>0.5937562537522514</v>
+        <v>0.5778784874663645</v>
       </c>
       <c r="AI2">
-        <v>0.6171820829288587</v>
+        <v>0.5762951245692334</v>
       </c>
       <c r="AJ2">
-        <v>0.4861626729665879</v>
+        <v>0.3234519702197203</v>
       </c>
       <c r="AK2">
-        <v>0.5106797837454577</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="E3">
-        <v>0.205</v>
+        <v>0.228</v>
+      </c>
+      <c r="F3">
+        <v>0.147</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>225.3</v>
+        <v>343.6</v>
       </c>
       <c r="L3">
-        <v>0.5280056245605812</v>
+        <v>0.5545513234344739</v>
       </c>
       <c r="M3">
-        <v>34.86</v>
+        <v>89.38</v>
       </c>
       <c r="N3">
-        <v>0.02862068965517241</v>
+        <v>0.05997450177816547</v>
       </c>
       <c r="O3">
-        <v>0.1547270306258322</v>
+        <v>0.260128055878929</v>
       </c>
       <c r="P3">
-        <v>26.7</v>
+        <v>89.38</v>
       </c>
       <c r="Q3">
-        <v>0.02192118226600985</v>
+        <v>0.05997450177816547</v>
       </c>
       <c r="R3">
-        <v>0.118508655126498</v>
+        <v>0.260128055878929</v>
       </c>
       <c r="S3">
-        <v>8.16</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.23407917383821</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>627.8</v>
+        <v>1327.7</v>
       </c>
       <c r="V3">
-        <v>0.5154351395730705</v>
+        <v>0.8908944507817219</v>
       </c>
       <c r="W3">
-        <v>0.263078000934143</v>
+        <v>0.3123068532994001</v>
       </c>
       <c r="X3">
-        <v>0.1074776879605195</v>
+        <v>0.1453327655588968</v>
       </c>
       <c r="Y3">
-        <v>0.1556003129736234</v>
+        <v>0.1669740877405033</v>
       </c>
       <c r="Z3">
-        <v>0.1820780883294218</v>
+        <v>0.2774245544909106</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0683454757985265</v>
+        <v>0.1064471554224178</v>
       </c>
       <c r="AC3">
-        <v>-0.0683454757985265</v>
+        <v>-0.1064471554224178</v>
       </c>
       <c r="AD3">
-        <v>1780.2</v>
+        <v>2040.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1780.2</v>
+        <v>2040.2</v>
       </c>
       <c r="AG3">
-        <v>1152.4</v>
+        <v>712.5</v>
       </c>
       <c r="AH3">
-        <v>0.5937562537522514</v>
+        <v>0.5778784874663645</v>
       </c>
       <c r="AI3">
-        <v>0.6171820829288587</v>
+        <v>0.5762951245692334</v>
       </c>
       <c r="AJ3">
-        <v>0.4861626729665879</v>
+        <v>0.3234519702197203</v>
       </c>
       <c r="AK3">
-        <v>0.5106797837454577</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/georgia/georgia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/georgia/georgia_bank_money_center.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.185</v>
+        <v>0.204</v>
       </c>
       <c r="E2">
-        <v>0.228</v>
-      </c>
-      <c r="F2">
-        <v>0.147</v>
+        <v>0.214</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>343.6</v>
+        <v>392.9</v>
       </c>
       <c r="L2">
-        <v>0.5545513234344739</v>
+        <v>0.484882142416389</v>
       </c>
       <c r="M2">
-        <v>89.38</v>
+        <v>111.315</v>
       </c>
       <c r="N2">
-        <v>0.05997450177816547</v>
+        <v>0.05690369082915856</v>
       </c>
       <c r="O2">
-        <v>0.260128055878929</v>
+        <v>0.2833163654874014</v>
       </c>
       <c r="P2">
-        <v>89.38</v>
+        <v>111.315</v>
       </c>
       <c r="Q2">
-        <v>0.05997450177816547</v>
+        <v>0.05690369082915856</v>
       </c>
       <c r="R2">
-        <v>0.260128055878929</v>
+        <v>0.2833163654874014</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1327.7</v>
+        <v>987.1</v>
       </c>
       <c r="V2">
-        <v>0.8908944507817219</v>
+        <v>0.5046007565688579</v>
       </c>
       <c r="W2">
-        <v>0.3123068532994001</v>
+        <v>0.2670427513083667</v>
       </c>
       <c r="X2">
-        <v>0.1453327655588968</v>
+        <v>0.1065901016799923</v>
       </c>
       <c r="Y2">
-        <v>0.1669740877405033</v>
+        <v>0.1604526496283745</v>
       </c>
       <c r="Z2">
-        <v>0.2774245544909106</v>
+        <v>0.3746705507005132</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1064471554224178</v>
+        <v>0.08820154084251111</v>
       </c>
       <c r="AC2">
-        <v>-0.1064471554224178</v>
+        <v>-0.08820154084251111</v>
       </c>
       <c r="AD2">
-        <v>2040.2</v>
+        <v>2102.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2040.2</v>
+        <v>2102.1</v>
       </c>
       <c r="AG2">
-        <v>712.5</v>
+        <v>1115</v>
       </c>
       <c r="AH2">
-        <v>0.5778784874663645</v>
+        <v>0.5179755069856836</v>
       </c>
       <c r="AI2">
-        <v>0.5762951245692334</v>
+        <v>0.5576897567187541</v>
       </c>
       <c r="AJ2">
-        <v>0.3234519702197203</v>
+        <v>0.3630502735087263</v>
       </c>
       <c r="AK2">
-        <v>0.3220338983050847</v>
+        <v>0.4007619869168285</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.185</v>
+        <v>0.204</v>
       </c>
       <c r="E3">
-        <v>0.228</v>
-      </c>
-      <c r="F3">
-        <v>0.147</v>
+        <v>0.214</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>343.6</v>
+        <v>392.9</v>
       </c>
       <c r="L3">
-        <v>0.5545513234344739</v>
+        <v>0.484882142416389</v>
       </c>
       <c r="M3">
-        <v>89.38</v>
+        <v>111.315</v>
       </c>
       <c r="N3">
-        <v>0.05997450177816547</v>
+        <v>0.05690369082915856</v>
       </c>
       <c r="O3">
-        <v>0.260128055878929</v>
+        <v>0.2833163654874014</v>
       </c>
       <c r="P3">
-        <v>89.38</v>
+        <v>111.315</v>
       </c>
       <c r="Q3">
-        <v>0.05997450177816547</v>
+        <v>0.05690369082915856</v>
       </c>
       <c r="R3">
-        <v>0.260128055878929</v>
+        <v>0.2833163654874014</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1327.7</v>
+        <v>987.1</v>
       </c>
       <c r="V3">
-        <v>0.8908944507817219</v>
+        <v>0.5046007565688579</v>
       </c>
       <c r="W3">
-        <v>0.3123068532994001</v>
+        <v>0.2670427513083667</v>
       </c>
       <c r="X3">
-        <v>0.1453327655588968</v>
+        <v>0.1065901016799923</v>
       </c>
       <c r="Y3">
-        <v>0.1669740877405033</v>
+        <v>0.1604526496283745</v>
       </c>
       <c r="Z3">
-        <v>0.2774245544909106</v>
+        <v>0.3746705507005132</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1064471554224178</v>
+        <v>0.08820154084251111</v>
       </c>
       <c r="AC3">
-        <v>-0.1064471554224178</v>
+        <v>-0.08820154084251111</v>
       </c>
       <c r="AD3">
-        <v>2040.2</v>
+        <v>2102.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2040.2</v>
+        <v>2102.1</v>
       </c>
       <c r="AG3">
-        <v>712.5</v>
+        <v>1115</v>
       </c>
       <c r="AH3">
-        <v>0.5778784874663645</v>
+        <v>0.5179755069856836</v>
       </c>
       <c r="AI3">
-        <v>0.5762951245692334</v>
+        <v>0.5576897567187541</v>
       </c>
       <c r="AJ3">
-        <v>0.3234519702197203</v>
+        <v>0.3630502735087263</v>
       </c>
       <c r="AK3">
-        <v>0.3220338983050847</v>
+        <v>0.4007619869168285</v>
       </c>
       <c r="AL3">
         <v>0</v>
